--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:43</t>
+    <t xml:space="preserve">2026-09-09 20:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:03</t>
+    <t xml:space="preserve">2026-09-18 17:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
@@ -30,33 +30,33 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallenar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copiapó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra Amarilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Tierra Amarilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freirina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copiapó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vallenar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:04</t>
+    <t xml:space="preserve">2026-09-27 21:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -486,13 +486,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4877</v>
+        <v>14000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5754</v>
+        <v>13149</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>84.76</v>
+        <v>106.47</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13018</v>
+        <v>20605</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14374</v>
+        <v>19612</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>90.57</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13151</v>
+        <v>11514</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14258</v>
+        <v>11374</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>92.24</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="5">
@@ -528,13 +528,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7389</v>
+        <v>57195</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7739</v>
+        <v>57224</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>95.48</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>57195</v>
+        <v>7389</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>57224</v>
+        <v>7739</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.95</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="8">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11514</v>
+        <v>13151</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11374</v>
+        <v>14258</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>101.23</v>
+        <v>92.24</v>
       </c>
     </row>
     <row r="9">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>20605</v>
+        <v>13018</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>19612</v>
+        <v>14374</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>105.06</v>
+        <v>90.57</v>
       </c>
     </row>
     <row r="10">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>14000</v>
+        <v>4877</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13149</v>
+        <v>5754</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>106.47</v>
+        <v>84.76</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_atacama.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:48</t>
+    <t xml:space="preserve">2026-10-05 05:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
